--- a/data/merged/2026-08-31/MERGED_UK_Mite-Vacuum_2026-08-31.xlsx
+++ b/data/merged/2026-08-31/MERGED_UK_Mite-Vacuum_2026-08-31.xlsx
@@ -2063,7 +2063,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR16"/>
+  <dimension ref="A1:BR15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -4694,40 +4694,40 @@
       <c r="B12" s="13"/>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>B0D5WTVR91</t>
+          <t>B0DSFM31F7</t>
         </is>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>OSALADI</t>
+          <t>Tjean</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Convenienceforyourhome/page/818AA347-F8E9-4151-B8B2-A1E50E5C29AE?lp_asin=B0D5WTVR91&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/stores/TJEANLifeCleanCookBette/page/D57A3099-B34A-4AE2-BEED-A573440938CE?lp_asin=B0DSFM31F7&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>OSALADI 3pcs Vacuum Wall Support Plastic Vacuum Holder for Wall Mounted Use Cordless Accessories Supports for Home Cleaning</t>
+          <t>Tjean UV Mattress Vacuum Cleaner,Futon Vacuum Dust Mite Vacuum – Dual Dust Bin, UV-C&amp;Ultrasonic Mite Removal, HEPA Filter, He</t>
         </is>
       </c>
       <c r="I12" s="14"/>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0D5WTVR91?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0DSFM31F7?psc=1</t>
         </is>
       </c>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/41-H5-VQSVL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71k7WLBBcwL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>B0D5WTVR91</t>
+          <t>B0DSFM31F7</t>
         </is>
       </c>
       <c r="M12" s="14" t="inlineStr">
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="O12" s="15">
-        <v>3767811</v>
+        <v>742501</v>
       </c>
       <c r="P12" s="15"/>
       <c r="Q12" s="16">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="S12" s="18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="T12" s="15"/>
@@ -4763,34 +4763,40 @@
       <c r="W12" s="15"/>
       <c r="X12" s="15"/>
       <c r="Y12" s="19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z12" s="20">
-        <v>20.99</v>
+        <v>46.8</v>
       </c>
       <c r="AA12"/>
       <c r="AB12"/>
       <c r="AC12" s="2"/>
-      <c r="AD12" s="19"/>
-      <c r="AE12" s="15"/>
-      <c r="AF12" s="21"/>
+      <c r="AD12" s="19">
+        <v>29</v>
+      </c>
+      <c r="AE12" s="15">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="21">
+        <v>4.6</v>
+      </c>
       <c r="AG12" s="22">
         <v>0</v>
       </c>
       <c r="AH12" s="20">
-        <v>2.74</v>
+        <v>3.42</v>
       </c>
       <c r="AI12" s="16">
-        <v>0.87</v>
+        <v>0.93</v>
       </c>
       <c r="AJ12"/>
       <c r="AK12" s="13" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AL12" s="19">
-        <v>765</v>
+        <v>501</v>
       </c>
       <c r="AM12" s="13" t="inlineStr">
         <is>
@@ -4800,13 +4806,15 @@
       <c r="AN12" s="13"/>
       <c r="AO12" s="13"/>
       <c r="AP12"/>
-      <c r="AQ12" s="19"/>
+      <c r="AQ12" s="19">
+        <v>10</v>
+      </c>
       <c r="AR12" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS12" s="14" t="inlineStr">
         <is>
-          <t>Original MJW</t>
+          <t>TJean Store</t>
         </is>
       </c>
       <c r="AT12" s="13" t="inlineStr">
@@ -4821,12 +4829,12 @@
       </c>
       <c r="AV12" s="14" t="inlineStr">
         <is>
-          <t>广州市 广东省 510650 CN</t>
+          <t>杭州市 余杭区 浙江省 311100 CN</t>
         </is>
       </c>
       <c r="AW12" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2BT6SVOQHN508</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A21G0QWAFKJ6UP</t>
         </is>
       </c>
       <c r="AX12" s="13"/>
@@ -4851,47 +4859,47 @@
       <c r="BI12" s="23"/>
       <c r="BJ12" s="23" t="inlineStr">
         <is>
-          <t>147 g</t>
+          <t>2.22 kg</t>
         </is>
       </c>
       <c r="BK12" s="23" t="inlineStr">
         <is>
-          <t>147.00 g</t>
+          <t>2.22 kg</t>
         </is>
       </c>
       <c r="BL12" s="23" t="inlineStr">
         <is>
-          <t>11 x 8.5 x 18 cm</t>
+          <t>24 x 19.5 x 28.5 cm</t>
         </is>
       </c>
       <c r="BM12" s="23" t="inlineStr">
         <is>
-          <t>11.00 x 8.50 x 18.00 cm</t>
+          <t>24.00 x 19.50 x 28.50 cm</t>
         </is>
       </c>
       <c r="BN12" s="23" t="inlineStr">
         <is>
-          <t>180 g</t>
+          <t>2.22 kg</t>
         </is>
       </c>
       <c r="BO12" s="23" t="inlineStr">
         <is>
-          <t>180.00 g</t>
+          <t>2.22 kg</t>
         </is>
       </c>
       <c r="BP12" s="23" t="inlineStr">
         <is>
-          <t>21 x 12 x 9 cm</t>
+          <t>32.6 x 27.5 x 21.1 cm</t>
         </is>
       </c>
       <c r="BQ12" s="23" t="inlineStr">
         <is>
-          <t>21.00 x 12.00 x 9.00 cm</t>
+          <t>32.60 x 27.50 x 21.10 cm</t>
         </is>
       </c>
       <c r="BR12" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -4902,40 +4910,40 @@
       <c r="B13" s="13"/>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>B0DSFM31F7</t>
+          <t>B0F1XRXLVK</t>
         </is>
       </c>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Tjean</t>
+          <t>Gxzsk</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/TJEANLifeCleanCookBette/page/D57A3099-B34A-4AE2-BEED-A573440938CE?lp_asin=B0DSFM31F7&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Gxzsk</t>
         </is>
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>Tjean UV Mattress Vacuum Cleaner,Futon Vacuum Dust Mite Vacuum – Dual Dust Bin, UV-C&amp;Ultrasonic Mite Removal, HEPA Filter, He</t>
+          <t>Gxzsk Mattress Vacuum Cleaner, 16kPa Bed Vacuum Cleaner with 253.7nm UV-C Light, Ultrasonic &amp; 140℉ Heating, Dual Cup &amp; Widen</t>
         </is>
       </c>
       <c r="I13" s="14"/>
       <c r="J13" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0DSFM31F7?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0F1XRXLVK?psc=1</t>
         </is>
       </c>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71k7WLBBcwL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/7185wuCbHrL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L13" s="14" t="inlineStr">
         <is>
-          <t>B0DSFM31F7</t>
+          <t>B0F1XRXLVK</t>
         </is>
       </c>
       <c r="M13" s="14" t="inlineStr">
@@ -4949,11 +4957,13 @@
         </is>
       </c>
       <c r="O13" s="15">
-        <v>742501</v>
-      </c>
-      <c r="P13" s="15"/>
+        <v>3492149</v>
+      </c>
+      <c r="P13" s="15">
+        <v>-21072</v>
+      </c>
       <c r="Q13" s="16">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="R13" s="17" t="inlineStr">
         <is>
@@ -4962,7 +4972,7 @@
       </c>
       <c r="S13" s="18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="T13" s="15"/>
@@ -4974,37 +4984,37 @@
         <v>1</v>
       </c>
       <c r="Z13" s="20">
-        <v>46.8</v>
+        <v>75.43</v>
       </c>
       <c r="AA13"/>
       <c r="AB13"/>
       <c r="AC13" s="2"/>
       <c r="AD13" s="19">
-        <v>29</v>
+        <v>364</v>
       </c>
       <c r="AE13" s="15">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF13" s="21">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AG13" s="22">
         <v>0</v>
       </c>
       <c r="AH13" s="20">
-        <v>3.42</v>
+        <v>3.59</v>
       </c>
       <c r="AI13" s="16">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="AJ13"/>
       <c r="AK13" s="13" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AL13" s="19">
-        <v>501</v>
+        <v>395</v>
       </c>
       <c r="AM13" s="13" t="inlineStr">
         <is>
@@ -5015,14 +5025,14 @@
       <c r="AO13" s="13"/>
       <c r="AP13"/>
       <c r="AQ13" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR13" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS13" s="14" t="inlineStr">
         <is>
-          <t>TJean Store</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT13" s="13" t="inlineStr">
@@ -5030,36 +5040,16 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="AU13" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV13" s="14" t="inlineStr">
-        <is>
-          <t>杭州市 余杭区 浙江省 311100 CN</t>
-        </is>
-      </c>
-      <c r="AW13" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A21G0QWAFKJ6UP</t>
-        </is>
-      </c>
+      <c r="AU13" s="13"/>
+      <c r="AV13" s="14"/>
+      <c r="AW13" s="13"/>
       <c r="AX13" s="13"/>
       <c r="AY13" s="13"/>
       <c r="AZ13" s="13"/>
       <c r="BA13" s="13"/>
       <c r="BB13" s="13"/>
-      <c r="BC13" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD13" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC13" s="13"/>
+      <c r="BD13" s="13"/>
       <c r="BE13" s="13"/>
       <c r="BF13" s="13"/>
       <c r="BG13" s="13"/>
@@ -5067,42 +5057,42 @@
       <c r="BI13" s="23"/>
       <c r="BJ13" s="23" t="inlineStr">
         <is>
-          <t>2.22 kg</t>
+          <t>2.16 kg</t>
         </is>
       </c>
       <c r="BK13" s="23" t="inlineStr">
         <is>
-          <t>2.22 kg</t>
+          <t>2.16 kg</t>
         </is>
       </c>
       <c r="BL13" s="23" t="inlineStr">
         <is>
-          <t>24 x 19.5 x 28.5 cm</t>
+          <t>25.1 x 29 x 14.7 cm</t>
         </is>
       </c>
       <c r="BM13" s="23" t="inlineStr">
         <is>
-          <t>24.00 x 19.50 x 28.50 cm</t>
+          <t>25.10 x 29.00 x 14.70 cm</t>
         </is>
       </c>
       <c r="BN13" s="23" t="inlineStr">
         <is>
-          <t>2.22 kg</t>
+          <t>2.16 kg</t>
         </is>
       </c>
       <c r="BO13" s="23" t="inlineStr">
         <is>
-          <t>2.22 kg</t>
+          <t>2.16 kg</t>
         </is>
       </c>
       <c r="BP13" s="23" t="inlineStr">
         <is>
-          <t>32.6 x 27.5 x 21.1 cm</t>
+          <t>32.4 x 29.3 x 17.2 cm</t>
         </is>
       </c>
       <c r="BQ13" s="23" t="inlineStr">
         <is>
-          <t>32.60 x 27.50 x 21.10 cm</t>
+          <t>32.40 x 29.30 x 17.20 cm</t>
         </is>
       </c>
       <c r="BR13" s="13" t="inlineStr">
@@ -5118,40 +5108,40 @@
       <c r="B14" s="13"/>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>B0F1XRXLVK</t>
+          <t>B0FHDW79RB</t>
         </is>
       </c>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Gxzsk</t>
+          <t>Generisch</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Gxzsk</t>
+          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Generisch</t>
         </is>
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>Gxzsk Mattress Vacuum Cleaner, 16kPa Bed Vacuum Cleaner with 253.7nm UV-C Light, Ultrasonic &amp; 140℉ Heating, Dual Cup &amp; Widen</t>
+          <t>Sofa Cleaner - Mattress Cleaner - Portable UV Bed Cleaning Vacuums24x24.5x11cm Portable Roller Brush Cleaning Machine | Rem</t>
         </is>
       </c>
       <c r="I14" s="14"/>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0F1XRXLVK?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FHDW79RB?psc=1</t>
         </is>
       </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/7185wuCbHrL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61cshoxTcWL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>B0F1XRXLVK</t>
+          <t>B0FHDW79RB</t>
         </is>
       </c>
       <c r="M14" s="14" t="inlineStr">
@@ -5165,13 +5155,11 @@
         </is>
       </c>
       <c r="O14" s="15">
-        <v>3492149</v>
-      </c>
-      <c r="P14" s="15">
-        <v>-21072</v>
-      </c>
+        <v>3543676</v>
+      </c>
+      <c r="P14" s="15"/>
       <c r="Q14" s="16">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R14" s="17" t="inlineStr">
         <is>
@@ -5180,7 +5168,7 @@
       </c>
       <c r="S14" s="18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="T14" s="15"/>
@@ -5192,37 +5180,31 @@
         <v>1</v>
       </c>
       <c r="Z14" s="20">
-        <v>75.43</v>
+        <v>21.19</v>
       </c>
       <c r="AA14"/>
       <c r="AB14"/>
       <c r="AC14" s="2"/>
-      <c r="AD14" s="19">
-        <v>364</v>
-      </c>
-      <c r="AE14" s="15">
-        <v>22</v>
-      </c>
-      <c r="AF14" s="21">
-        <v>4.4</v>
-      </c>
+      <c r="AD14" s="19"/>
+      <c r="AE14" s="15"/>
+      <c r="AF14" s="21"/>
       <c r="AG14" s="22">
         <v>0</v>
       </c>
       <c r="AH14" s="20">
-        <v>3.59</v>
+        <v>4.87</v>
       </c>
       <c r="AI14" s="16">
-        <v>0.95</v>
+        <v>0.77</v>
       </c>
       <c r="AJ14"/>
       <c r="AK14" s="13" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="AL14" s="19">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="AM14" s="13" t="inlineStr">
         <is>
@@ -5240,7 +5222,7 @@
       </c>
       <c r="AS14" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>BLESSSHNIA</t>
         </is>
       </c>
       <c r="AT14" s="13" t="inlineStr">
@@ -5248,15 +5230,31 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="AU14" s="13"/>
-      <c r="AV14" s="14"/>
-      <c r="AW14" s="13"/>
+      <c r="AU14" s="13" t="inlineStr">
+        <is>
+          <t>CN(HK)</t>
+        </is>
+      </c>
+      <c r="AV14" s="14" t="inlineStr">
+        <is>
+          <t>MONG KOK HONG KONG 0000 HK</t>
+        </is>
+      </c>
+      <c r="AW14" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2MUGEKSN5UHQP</t>
+        </is>
+      </c>
       <c r="AX14" s="13"/>
       <c r="AY14" s="13"/>
       <c r="AZ14" s="13"/>
       <c r="BA14" s="13"/>
       <c r="BB14" s="13"/>
-      <c r="BC14" s="13"/>
+      <c r="BC14" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD14" s="13"/>
       <c r="BE14" s="13"/>
       <c r="BF14" s="13"/>
@@ -5265,49 +5263,29 @@
       <c r="BI14" s="23"/>
       <c r="BJ14" s="23" t="inlineStr">
         <is>
-          <t>2.16 kg</t>
+          <t>983 g</t>
         </is>
       </c>
       <c r="BK14" s="23" t="inlineStr">
         <is>
-          <t>2.16 kg</t>
+          <t>983.00 g</t>
         </is>
       </c>
       <c r="BL14" s="23" t="inlineStr">
         <is>
-          <t>25.1 x 29 x 14.7 cm</t>
+          <t>30.2 x 28.7 x 16 cm</t>
         </is>
       </c>
       <c r="BM14" s="23" t="inlineStr">
         <is>
-          <t>25.10 x 29.00 x 14.70 cm</t>
-        </is>
-      </c>
-      <c r="BN14" s="23" t="inlineStr">
-        <is>
-          <t>2.16 kg</t>
-        </is>
-      </c>
-      <c r="BO14" s="23" t="inlineStr">
-        <is>
-          <t>2.16 kg</t>
-        </is>
-      </c>
-      <c r="BP14" s="23" t="inlineStr">
-        <is>
-          <t>32.4 x 29.3 x 17.2 cm</t>
-        </is>
-      </c>
-      <c r="BQ14" s="23" t="inlineStr">
-        <is>
-          <t>32.40 x 29.30 x 17.20 cm</t>
-        </is>
-      </c>
-      <c r="BR14" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
+          <t>30.20 x 28.70 x 16.00 cm</t>
+        </is>
+      </c>
+      <c r="BN14" s="23"/>
+      <c r="BO14" s="23"/>
+      <c r="BP14" s="23"/>
+      <c r="BQ14" s="23"/>
+      <c r="BR14" s="13"/>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13">
@@ -5316,40 +5294,40 @@
       <c r="B15" s="13"/>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>B0FHDW79RB</t>
+          <t>B0FPQMRBYZ</t>
         </is>
       </c>
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Generisch</t>
+          <t>KÄRCHER</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Generisch</t>
+          <t>https://www.amazon.co.uk/stores/K%C3%A4rcherUK/page/F6053778-BFEE-41CB-9B1B-A16ECF7857D7?lp_asin=B0FPQMRBYZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>Sofa Cleaner - Mattress Cleaner - Portable UV Bed Cleaning Vacuums24x24.5x11cm Portable Roller Brush Cleaning Machine | Rem</t>
+          <t>Kärcher Mattress cleaner VCH 4 UVClean, hygienic deep cleaning with UV-C light, knock roller and suction function, power 500</t>
         </is>
       </c>
       <c r="I15" s="14"/>
       <c r="J15" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FHDW79RB?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FPQMRBYZ?psc=1</t>
         </is>
       </c>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61cshoxTcWL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81MMJHIRoeL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L15" s="14" t="inlineStr">
         <is>
-          <t>B0FHDW79RB</t>
+          <t>B0FPQMRBYZ</t>
         </is>
       </c>
       <c r="M15" s="14" t="inlineStr">
@@ -5363,11 +5341,13 @@
         </is>
       </c>
       <c r="O15" s="15">
-        <v>3543676</v>
-      </c>
-      <c r="P15" s="15"/>
+        <v>1447886</v>
+      </c>
+      <c r="P15" s="15">
+        <v>-124330</v>
+      </c>
       <c r="Q15" s="16">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="R15" s="17" t="inlineStr">
         <is>
@@ -5376,11 +5356,13 @@
       </c>
       <c r="S15" s="18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="T15" s="15"/>
-      <c r="U15" s="16"/>
+      <c r="U15" s="16">
+        <v>-0.43</v>
+      </c>
       <c r="V15" s="15"/>
       <c r="W15" s="15"/>
       <c r="X15" s="15"/>
@@ -5388,69 +5370,75 @@
         <v>1</v>
       </c>
       <c r="Z15" s="20">
-        <v>21.19</v>
+        <v>160</v>
       </c>
       <c r="AA15"/>
       <c r="AB15"/>
       <c r="AC15" s="2"/>
-      <c r="AD15" s="19"/>
-      <c r="AE15" s="15"/>
-      <c r="AF15" s="21"/>
+      <c r="AD15" s="19">
+        <v>178</v>
+      </c>
+      <c r="AE15" s="15">
+        <v>33</v>
+      </c>
+      <c r="AF15" s="21">
+        <v>4.6</v>
+      </c>
       <c r="AG15" s="22">
         <v>0</v>
       </c>
       <c r="AH15" s="20">
-        <v>4.87</v>
+        <v>3.43</v>
       </c>
       <c r="AI15" s="16">
-        <v>0.77</v>
+        <v>0.97</v>
       </c>
       <c r="AJ15"/>
       <c r="AK15" s="13" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL15" s="19">
-        <v>413</v>
+        <v>270</v>
       </c>
       <c r="AM15" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN15" s="13"/>
       <c r="AO15" s="13"/>
       <c r="AP15"/>
       <c r="AQ15" s="19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR15" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS15" s="14" t="inlineStr">
         <is>
-          <t>BLESSSHNIA</t>
+          <t>PhutureTech</t>
         </is>
       </c>
       <c r="AT15" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU15" s="13" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="AV15" s="14" t="inlineStr">
         <is>
-          <t>MONG KOK HONG KONG 0000 HK</t>
+          <t>Stourbridge West Midlands DY9 7AT GB</t>
         </is>
       </c>
       <c r="AW15" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2MUGEKSN5UHQP</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3BE2QBOLZR1UZ</t>
         </is>
       </c>
       <c r="AX15" s="13"/>
@@ -5458,11 +5446,7 @@
       <c r="AZ15" s="13"/>
       <c r="BA15" s="13"/>
       <c r="BB15" s="13"/>
-      <c r="BC15" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC15" s="13"/>
       <c r="BD15" s="13"/>
       <c r="BE15" s="13"/>
       <c r="BF15" s="13"/>
@@ -5471,237 +5455,45 @@
       <c r="BI15" s="23"/>
       <c r="BJ15" s="23" t="inlineStr">
         <is>
-          <t>983 g</t>
+          <t>2.5 kg</t>
         </is>
       </c>
       <c r="BK15" s="23" t="inlineStr">
         <is>
-          <t>983.00 g</t>
+          <t>2.50 kg</t>
         </is>
       </c>
       <c r="BL15" s="23" t="inlineStr">
         <is>
-          <t>30.2 x 28.7 x 16 cm</t>
+          <t>30.9 x 24 x 17 cm</t>
         </is>
       </c>
       <c r="BM15" s="23" t="inlineStr">
         <is>
-          <t>30.20 x 28.70 x 16.00 cm</t>
-        </is>
-      </c>
-      <c r="BN15" s="23"/>
-      <c r="BO15" s="23"/>
-      <c r="BP15" s="23"/>
-      <c r="BQ15" s="23"/>
-      <c r="BR15" s="13"/>
-    </row>
-    <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="13">
-        <v>15</v>
-      </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>B0FPQMRBYZ</t>
-        </is>
-      </c>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14" t="inlineStr">
-        <is>
-          <t>KÄRCHER</t>
-        </is>
-      </c>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/stores/K%C3%A4rcherUK/page/F6053778-BFEE-41CB-9B1B-A16ECF7857D7?lp_asin=B0FPQMRBYZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H16" s="14" t="inlineStr">
-        <is>
-          <t>Kärcher Mattress cleaner VCH 4 UVClean, hygienic deep cleaning with UV-C light, knock roller and suction function, power 500</t>
-        </is>
-      </c>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/dp/B0FPQMRBYZ?psc=1</t>
-        </is>
-      </c>
-      <c r="K16" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81MMJHIRoeL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L16" s="14" t="inlineStr">
-        <is>
-          <t>B0FPQMRBYZ</t>
-        </is>
-      </c>
-      <c r="M16" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen:Kitchen &amp; Home Appliances:Vacuums &amp; Floor Care:Vacuums:Futon Vacuums</t>
-        </is>
-      </c>
-      <c r="N16" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen</t>
-        </is>
-      </c>
-      <c r="O16" s="15">
-        <v>1447886</v>
-      </c>
-      <c r="P16" s="15">
-        <v>-124330</v>
-      </c>
-      <c r="Q16" s="16">
-        <v>-0.09</v>
-      </c>
-      <c r="R16" s="17" t="inlineStr">
-        <is>
-          <t>Futon Vacuums</t>
-        </is>
-      </c>
-      <c r="S16" s="18" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="T16" s="15"/>
-      <c r="U16" s="16">
-        <v>-0.43</v>
-      </c>
-      <c r="V16" s="15"/>
-      <c r="W16" s="15"/>
-      <c r="X16" s="15"/>
-      <c r="Y16" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z16" s="20">
-        <v>160</v>
-      </c>
-      <c r="AA16"/>
-      <c r="AB16"/>
-      <c r="AC16" s="2"/>
-      <c r="AD16" s="19">
-        <v>178</v>
-      </c>
-      <c r="AE16" s="15">
-        <v>33</v>
-      </c>
-      <c r="AF16" s="21">
-        <v>4.6</v>
-      </c>
-      <c r="AG16" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH16" s="20">
-        <v>3.43</v>
-      </c>
-      <c r="AI16" s="16">
-        <v>0.97</v>
-      </c>
-      <c r="AJ16"/>
-      <c r="AK16" s="13" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AL16" s="19">
-        <v>270</v>
-      </c>
-      <c r="AM16" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AN16" s="13"/>
-      <c r="AO16" s="13"/>
-      <c r="AP16"/>
-      <c r="AQ16" s="19">
-        <v>9</v>
-      </c>
-      <c r="AR16" s="19">
-        <v>2</v>
-      </c>
-      <c r="AS16" s="14" t="inlineStr">
-        <is>
-          <t>PhutureTech</t>
-        </is>
-      </c>
-      <c r="AT16" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU16" s="13" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="AV16" s="14" t="inlineStr">
-        <is>
-          <t>Stourbridge West Midlands DY9 7AT GB</t>
-        </is>
-      </c>
-      <c r="AW16" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3BE2QBOLZR1UZ</t>
-        </is>
-      </c>
-      <c r="AX16" s="13"/>
-      <c r="AY16" s="13"/>
-      <c r="AZ16" s="13"/>
-      <c r="BA16" s="13"/>
-      <c r="BB16" s="13"/>
-      <c r="BC16" s="13"/>
-      <c r="BD16" s="13"/>
-      <c r="BE16" s="13"/>
-      <c r="BF16" s="13"/>
-      <c r="BG16" s="13"/>
-      <c r="BH16" s="14"/>
-      <c r="BI16" s="23"/>
-      <c r="BJ16" s="23" t="inlineStr">
-        <is>
-          <t>2.5 kg</t>
-        </is>
-      </c>
-      <c r="BK16" s="23" t="inlineStr">
-        <is>
-          <t>2.50 kg</t>
-        </is>
-      </c>
-      <c r="BL16" s="23" t="inlineStr">
-        <is>
-          <t>30.9 x 24 x 17 cm</t>
-        </is>
-      </c>
-      <c r="BM16" s="23" t="inlineStr">
-        <is>
           <t>30.90 x 24.00 x 17.00 cm</t>
         </is>
       </c>
-      <c r="BN16" s="23" t="inlineStr">
+      <c r="BN15" s="23" t="inlineStr">
         <is>
           <t>3.2 kg</t>
         </is>
       </c>
-      <c r="BO16" s="23" t="inlineStr">
+      <c r="BO15" s="23" t="inlineStr">
         <is>
           <t>3.20 kg</t>
         </is>
       </c>
-      <c r="BP16" s="23" t="inlineStr">
+      <c r="BP15" s="23" t="inlineStr">
         <is>
           <t>39.1 x 29.4 x 19.3 cm</t>
         </is>
       </c>
-      <c r="BQ16" s="23" t="inlineStr">
+      <c r="BQ15" s="23" t="inlineStr">
         <is>
           <t>39.10 x 29.40 x 19.30 cm</t>
         </is>
       </c>
-      <c r="BR16" s="13" t="inlineStr">
+      <c r="BR15" s="13" t="inlineStr">
         <is>
           <t>标准包裹</t>
         </is>
@@ -5789,385 +5581,43 @@
     <hyperlink ref="L11" r:id="rId76" tooltip="https://www.amazon.co.uk/dp/B0D1QQXH6V"/>
     <hyperlink ref="M11" r:id="rId77" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
     <hyperlink ref="N11" r:id="rId78"/>
-    <hyperlink ref="C12" r:id="rId79" tooltip="https://www.amazon.co.uk/dp/B0D5WTVR91"/>
-    <hyperlink ref="G12" r:id="rId80" tooltip="https://www.amazon.co.uk/stores/Convenienceforyourhome/page/818AA347-F8E9-4151-B8B2-A1E50E5C29AE?lp_asin=B0D5WTVR91&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J12" r:id="rId81" tooltip="https://www.amazon.co.uk/dp/B0D5WTVR91?psc=1"/>
-    <hyperlink ref="K12" r:id="rId82" tooltip="https://images-na.ssl-images-amazon.com/images/I/41-H5-VQSVL._AC_US600_.jpg"/>
-    <hyperlink ref="L12" r:id="rId83" tooltip="https://www.amazon.co.uk/dp/B0D5WTVR91"/>
+    <hyperlink ref="C12" r:id="rId79" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7"/>
+    <hyperlink ref="G12" r:id="rId80" tooltip="https://www.amazon.co.uk/stores/TJEANLifeCleanCookBette/page/D57A3099-B34A-4AE2-BEED-A573440938CE?lp_asin=B0DSFM31F7&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J12" r:id="rId81" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7?psc=1"/>
+    <hyperlink ref="K12" r:id="rId82" tooltip="https://images-na.ssl-images-amazon.com/images/I/71k7WLBBcwL._AC_US600_.jpg"/>
+    <hyperlink ref="L12" r:id="rId83" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7"/>
     <hyperlink ref="M12" r:id="rId84" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
     <hyperlink ref="N12" r:id="rId85"/>
-    <hyperlink ref="AW12" r:id="rId86" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2BT6SVOQHN508"/>
-    <hyperlink ref="C13" r:id="rId87" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7"/>
-    <hyperlink ref="G13" r:id="rId88" tooltip="https://www.amazon.co.uk/stores/TJEANLifeCleanCookBette/page/D57A3099-B34A-4AE2-BEED-A573440938CE?lp_asin=B0DSFM31F7&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J13" r:id="rId89" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7?psc=1"/>
-    <hyperlink ref="K13" r:id="rId90" tooltip="https://images-na.ssl-images-amazon.com/images/I/71k7WLBBcwL._AC_US600_.jpg"/>
-    <hyperlink ref="L13" r:id="rId91" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7"/>
+    <hyperlink ref="AW12" r:id="rId86" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A21G0QWAFKJ6UP"/>
+    <hyperlink ref="C13" r:id="rId87" tooltip="https://www.amazon.co.uk/dp/B0F1XRXLVK"/>
+    <hyperlink ref="G13" r:id="rId88" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Gxzsk"/>
+    <hyperlink ref="J13" r:id="rId89" tooltip="https://www.amazon.co.uk/dp/B0F1XRXLVK?psc=1"/>
+    <hyperlink ref="K13" r:id="rId90" tooltip="https://images-na.ssl-images-amazon.com/images/I/7185wuCbHrL._AC_US600_.jpg"/>
+    <hyperlink ref="L13" r:id="rId91" tooltip="https://www.amazon.co.uk/dp/B0F1XRXLVK"/>
     <hyperlink ref="M13" r:id="rId92" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
     <hyperlink ref="N13" r:id="rId93"/>
-    <hyperlink ref="AW13" r:id="rId94" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A21G0QWAFKJ6UP"/>
-    <hyperlink ref="C14" r:id="rId95" tooltip="https://www.amazon.co.uk/dp/B0F1XRXLVK"/>
-    <hyperlink ref="G14" r:id="rId96" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Gxzsk"/>
-    <hyperlink ref="J14" r:id="rId97" tooltip="https://www.amazon.co.uk/dp/B0F1XRXLVK?psc=1"/>
-    <hyperlink ref="K14" r:id="rId98" tooltip="https://images-na.ssl-images-amazon.com/images/I/7185wuCbHrL._AC_US600_.jpg"/>
-    <hyperlink ref="L14" r:id="rId99" tooltip="https://www.amazon.co.uk/dp/B0F1XRXLVK"/>
-    <hyperlink ref="M14" r:id="rId100" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
-    <hyperlink ref="N14" r:id="rId101"/>
-    <hyperlink ref="C15" r:id="rId102" tooltip="https://www.amazon.co.uk/dp/B0FHDW79RB"/>
-    <hyperlink ref="G15" r:id="rId103" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Generisch"/>
-    <hyperlink ref="J15" r:id="rId104" tooltip="https://www.amazon.co.uk/dp/B0FHDW79RB?psc=1"/>
-    <hyperlink ref="K15" r:id="rId105" tooltip="https://images-na.ssl-images-amazon.com/images/I/61cshoxTcWL._AC_US600_.jpg"/>
-    <hyperlink ref="L15" r:id="rId106" tooltip="https://www.amazon.co.uk/dp/B0FHDW79RB"/>
+    <hyperlink ref="C14" r:id="rId94" tooltip="https://www.amazon.co.uk/dp/B0FHDW79RB"/>
+    <hyperlink ref="G14" r:id="rId95" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Generisch"/>
+    <hyperlink ref="J14" r:id="rId96" tooltip="https://www.amazon.co.uk/dp/B0FHDW79RB?psc=1"/>
+    <hyperlink ref="K14" r:id="rId97" tooltip="https://images-na.ssl-images-amazon.com/images/I/61cshoxTcWL._AC_US600_.jpg"/>
+    <hyperlink ref="L14" r:id="rId98" tooltip="https://www.amazon.co.uk/dp/B0FHDW79RB"/>
+    <hyperlink ref="M14" r:id="rId99" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
+    <hyperlink ref="N14" r:id="rId100"/>
+    <hyperlink ref="AW14" r:id="rId101" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2MUGEKSN5UHQP"/>
+    <hyperlink ref="C15" r:id="rId102" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ"/>
+    <hyperlink ref="G15" r:id="rId103" tooltip="https://www.amazon.co.uk/stores/K%C3%A4rcherUK/page/F6053778-BFEE-41CB-9B1B-A16ECF7857D7?lp_asin=B0FPQMRBYZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J15" r:id="rId104" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ?psc=1"/>
+    <hyperlink ref="K15" r:id="rId105" tooltip="https://images-na.ssl-images-amazon.com/images/I/81MMJHIRoeL._AC_US600_.jpg"/>
+    <hyperlink ref="L15" r:id="rId106" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ"/>
     <hyperlink ref="M15" r:id="rId107" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
     <hyperlink ref="N15" r:id="rId108"/>
-    <hyperlink ref="AW15" r:id="rId109" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2MUGEKSN5UHQP"/>
-    <hyperlink ref="C16" r:id="rId110" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ"/>
-    <hyperlink ref="G16" r:id="rId111" tooltip="https://www.amazon.co.uk/stores/K%C3%A4rcherUK/page/F6053778-BFEE-41CB-9B1B-A16ECF7857D7?lp_asin=B0FPQMRBYZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J16" r:id="rId112" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ?psc=1"/>
-    <hyperlink ref="K16" r:id="rId113" tooltip="https://images-na.ssl-images-amazon.com/images/I/81MMJHIRoeL._AC_US600_.jpg"/>
-    <hyperlink ref="L16" r:id="rId114" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ"/>
-    <hyperlink ref="M16" r:id="rId115" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
-    <hyperlink ref="N16" r:id="rId116"/>
-    <hyperlink ref="AW16" r:id="rId117" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3BE2QBOLZR1UZ"/>
+    <hyperlink ref="AW15" r:id="rId109" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3BE2QBOLZR1UZ"/>
   </hyperlinks>
-  <drawing r:id="rId118"/>
+  <drawing r:id="rId110"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="25" style="1" customWidth="1"/>
-    <col min="2" max="5" width="13" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10" style="4" customWidth="1"/>
-    <col min="7" max="7" width="10" style="6" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>品牌</t>
-        </is>
-      </c>
-      <c r="B1" s="8" t="inlineStr">
-        <is>
-          <t>月销量</t>
-        </is>
-      </c>
-      <c r="C1" s="8" t="inlineStr">
-        <is>
-          <t>月销售额(£)</t>
-        </is>
-      </c>
-      <c r="D1" s="8" t="inlineStr">
-        <is>
-          <t>近1年销量</t>
-        </is>
-      </c>
-      <c r="E1" s="8" t="inlineStr">
-        <is>
-          <t>近一年销售额(£)</t>
-        </is>
-      </c>
-      <c r="F1" s="10" t="inlineStr">
-        <is>
-          <t>平均价格(£)</t>
-        </is>
-      </c>
-      <c r="G1" s="12" t="inlineStr">
-        <is>
-          <t>市场份额</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Hoover</t>
-        </is>
-      </c>
-      <c r="B2" s="15">
-        <v>568</v>
-      </c>
-      <c r="C2" s="15">
-        <v>42856</v>
-      </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="20">
-        <v>75.45070422535211</v>
-      </c>
-      <c r="G2" s="22">
-        <v>0.7153652392947103</v>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>Jimmy</t>
-        </is>
-      </c>
-      <c r="B3" s="15">
-        <v>93</v>
-      </c>
-      <c r="C3" s="15">
-        <v>15809</v>
-      </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="20">
-        <v>169.98924731182797</v>
-      </c>
-      <c r="G3" s="22">
-        <v>0.11712846347607053</v>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>Teant</t>
-        </is>
-      </c>
-      <c r="B4" s="15">
-        <v>81</v>
-      </c>
-      <c r="C4" s="15">
-        <v>5851</v>
-      </c>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="20">
-        <v>72.23456790123457</v>
-      </c>
-      <c r="G4" s="22">
-        <v>0.10201511335012595</v>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>HAUSHOF</t>
-        </is>
-      </c>
-      <c r="B5" s="15">
-        <v>35</v>
-      </c>
-      <c r="C5" s="15">
-        <v>1911</v>
-      </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="20">
-        <v>54.6</v>
-      </c>
-      <c r="G5" s="22">
-        <v>0.04408060453400504</v>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>RANVOO</t>
-        </is>
-      </c>
-      <c r="B6" s="15">
-        <v>10</v>
-      </c>
-      <c r="C6" s="15">
-        <v>1590</v>
-      </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="20">
-        <v>159.0</v>
-      </c>
-      <c r="G6" s="22">
-        <v>0.012594458438287154</v>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>Minthouz</t>
-        </is>
-      </c>
-      <c r="B7" s="15">
-        <v>4</v>
-      </c>
-      <c r="C7" s="15">
-        <v>238</v>
-      </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="20">
-        <v>59.5</v>
-      </c>
-      <c r="G7" s="22">
-        <v>0.005037783375314861</v>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="B8" s="15">
-        <v>3</v>
-      </c>
-      <c r="C8" s="15">
-        <v>135</v>
-      </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="20">
-        <v>45.0</v>
-      </c>
-      <c r="G8" s="22">
-        <v>0.003778337531486146</v>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>Amzany</t>
-        </is>
-      </c>
-      <c r="B9" s="15">
-        <v>0</v>
-      </c>
-      <c r="C9" s="15">
-        <v>0</v>
-      </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>Generisch</t>
-        </is>
-      </c>
-      <c r="B10" s="15">
-        <v>0</v>
-      </c>
-      <c r="C10" s="15">
-        <v>0</v>
-      </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>Gxzsk</t>
-        </is>
-      </c>
-      <c r="B11" s="15">
-        <v>0</v>
-      </c>
-      <c r="C11" s="15">
-        <v>0</v>
-      </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>JIGOO</t>
-        </is>
-      </c>
-      <c r="B12" s="15">
-        <v>0</v>
-      </c>
-      <c r="C12" s="15">
-        <v>0</v>
-      </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>KÄRCHER</t>
-        </is>
-      </c>
-      <c r="B13" s="15">
-        <v>0</v>
-      </c>
-      <c r="C13" s="15">
-        <v>0</v>
-      </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>OSALADI</t>
-        </is>
-      </c>
-      <c r="B14" s="15">
-        <v>0</v>
-      </c>
-      <c r="C14" s="15">
-        <v>0</v>
-      </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>Tjean</t>
-        </is>
-      </c>
-      <c r="B15" s="15">
-        <v>0</v>
-      </c>
-      <c r="C15" s="15">
-        <v>0</v>
-      </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -6181,7 +5631,7 @@
     <row r="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>卖家</t>
+          <t>品牌</t>
         </is>
       </c>
       <c r="B1" s="8" t="inlineStr">
@@ -6218,7 +5668,7 @@
     <row r="2" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Family Run Business (VAT CHARGED)</t>
+          <t>Hoover</t>
         </is>
       </c>
       <c r="B2" s="15">
@@ -6239,7 +5689,7 @@
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>MINTERZ</t>
+          <t>Jimmy</t>
         </is>
       </c>
       <c r="B3" s="15">
@@ -6281,7 +5731,7 @@
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>TS.Werkzeug</t>
+          <t>HAUSHOF</t>
         </is>
       </c>
       <c r="B5" s="15">
@@ -6302,7 +5752,7 @@
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>RANVOO Official UK</t>
+          <t>RANVOO</t>
         </is>
       </c>
       <c r="B6" s="15">
@@ -6323,7 +5773,7 @@
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Minthouz</t>
         </is>
       </c>
       <c r="B7" s="15">
@@ -6344,7 +5794,7 @@
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>Bear Official Store</t>
+          <t>Bear</t>
         </is>
       </c>
       <c r="B8" s="15">
@@ -6365,7 +5815,7 @@
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>Amazon US</t>
+          <t>Amzany</t>
         </is>
       </c>
       <c r="B9" s="15">
@@ -6384,7 +5834,7 @@
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>BLESSSHNIA</t>
+          <t>Generisch</t>
         </is>
       </c>
       <c r="B10" s="15">
@@ -6403,7 +5853,7 @@
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>Original MJW</t>
+          <t>Gxzsk</t>
         </is>
       </c>
       <c r="B11" s="15">
@@ -6422,7 +5872,7 @@
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>PhutureTech</t>
+          <t>JIGOO</t>
         </is>
       </c>
       <c r="B12" s="15">
@@ -6441,7 +5891,7 @@
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>TJean Store</t>
+          <t>KÄRCHER</t>
         </is>
       </c>
       <c r="B13" s="15">
@@ -6460,7 +5910,7 @@
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>Tengke-EU</t>
+          <t>Tjean</t>
         </is>
       </c>
       <c r="B14" s="15">
@@ -6473,6 +5923,302 @@
       <c r="E14" s="15"/>
       <c r="F14" s="20"/>
       <c r="G14" s="22">
+        <v>0.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="25" style="1" customWidth="1"/>
+    <col min="2" max="5" width="13" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10" style="4" customWidth="1"/>
+    <col min="7" max="7" width="10" style="6" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>卖家</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>月销量</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>月销售额(£)</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>近1年销量</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>近一年销售额(£)</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>平均价格(£)</t>
+        </is>
+      </c>
+      <c r="G1" s="12" t="inlineStr">
+        <is>
+          <t>市场份额</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Family Run Business (VAT CHARGED)</t>
+        </is>
+      </c>
+      <c r="B2" s="15">
+        <v>568</v>
+      </c>
+      <c r="C2" s="15">
+        <v>42856</v>
+      </c>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="20">
+        <v>75.45070422535211</v>
+      </c>
+      <c r="G2" s="22">
+        <v>0.7153652392947103</v>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>MINTERZ</t>
+        </is>
+      </c>
+      <c r="B3" s="15">
+        <v>93</v>
+      </c>
+      <c r="C3" s="15">
+        <v>15809</v>
+      </c>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="20">
+        <v>169.98924731182797</v>
+      </c>
+      <c r="G3" s="22">
+        <v>0.11712846347607053</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Teant</t>
+        </is>
+      </c>
+      <c r="B4" s="15">
+        <v>81</v>
+      </c>
+      <c r="C4" s="15">
+        <v>5851</v>
+      </c>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="20">
+        <v>72.23456790123457</v>
+      </c>
+      <c r="G4" s="22">
+        <v>0.10201511335012595</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>TS.Werkzeug</t>
+        </is>
+      </c>
+      <c r="B5" s="15">
+        <v>35</v>
+      </c>
+      <c r="C5" s="15">
+        <v>1911</v>
+      </c>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="20">
+        <v>54.6</v>
+      </c>
+      <c r="G5" s="22">
+        <v>0.04408060453400504</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>RANVOO Official UK</t>
+        </is>
+      </c>
+      <c r="B6" s="15">
+        <v>10</v>
+      </c>
+      <c r="C6" s="15">
+        <v>1590</v>
+      </c>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="20">
+        <v>159.0</v>
+      </c>
+      <c r="G6" s="22">
+        <v>0.012594458438287154</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B7" s="15">
+        <v>4</v>
+      </c>
+      <c r="C7" s="15">
+        <v>238</v>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="20">
+        <v>59.5</v>
+      </c>
+      <c r="G7" s="22">
+        <v>0.005037783375314861</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Bear Official Store</t>
+        </is>
+      </c>
+      <c r="B8" s="15">
+        <v>3</v>
+      </c>
+      <c r="C8" s="15">
+        <v>135</v>
+      </c>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="20">
+        <v>45.0</v>
+      </c>
+      <c r="G8" s="22">
+        <v>0.003778337531486146</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Amazon US</t>
+        </is>
+      </c>
+      <c r="B9" s="15">
+        <v>0</v>
+      </c>
+      <c r="C9" s="15">
+        <v>0</v>
+      </c>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="22">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>BLESSSHNIA</t>
+        </is>
+      </c>
+      <c r="B10" s="15">
+        <v>0</v>
+      </c>
+      <c r="C10" s="15">
+        <v>0</v>
+      </c>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="22">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>PhutureTech</t>
+        </is>
+      </c>
+      <c r="B11" s="15">
+        <v>0</v>
+      </c>
+      <c r="C11" s="15">
+        <v>0</v>
+      </c>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="22">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>TJean Store</t>
+        </is>
+      </c>
+      <c r="B12" s="15">
+        <v>0</v>
+      </c>
+      <c r="C12" s="15">
+        <v>0</v>
+      </c>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="22">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Tengke-EU</t>
+        </is>
+      </c>
+      <c r="B13" s="15">
+        <v>0</v>
+      </c>
+      <c r="C13" s="15">
+        <v>0</v>
+      </c>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="22">
         <v>0.0</v>
       </c>
     </row>
